--- a/saidas/metricas_resumo/valor/5_b_top_5/parte_2_janeiro_em_diante.xlsx
+++ b/saidas/metricas_resumo/valor/5_b_top_5/parte_2_janeiro_em_diante.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Modelo</t>
   </si>
@@ -49,49 +49,34 @@
     <t>SARIMA</t>
   </si>
   <si>
-    <t>ExtraTrees(EXT,j90)</t>
-  </si>
-  <si>
-    <t>POLY+ABR</t>
+    <t>VotingRegressor (RandomForest + ExtraTrees + XGBoost)</t>
   </si>
   <si>
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
-    <t>Voting(GBR+XGB+RFR)</t>
-  </si>
-  <si>
-    <t>26/55</t>
-  </si>
-  <si>
-    <t>27/55</t>
-  </si>
-  <si>
-    <t>22/55</t>
-  </si>
-  <si>
-    <t>28/56</t>
-  </si>
-  <si>
-    <t>24/55</t>
-  </si>
-  <si>
-    <t>45/55</t>
-  </si>
-  <si>
-    <t>43/55</t>
-  </si>
-  <si>
-    <t>40/55</t>
-  </si>
-  <si>
-    <t>37/56</t>
-  </si>
-  <si>
-    <t>55/55</t>
-  </si>
-  <si>
-    <t>56/56</t>
+    <t>37/70</t>
+  </si>
+  <si>
+    <t>34/70</t>
+  </si>
+  <si>
+    <t>26/71</t>
+  </si>
+  <si>
+    <t>58/70</t>
+  </si>
+  <si>
+    <t>54/70</t>
+  </si>
+  <si>
+    <t>43/71</t>
+  </si>
+  <si>
+    <t>70/70</t>
+  </si>
+  <si>
+    <t>71/71</t>
   </si>
 </sst>
 </file>
@@ -449,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -489,31 +474,31 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>6.07</v>
+        <v>5.65</v>
       </c>
       <c r="C2">
-        <v>8.43</v>
+        <v>7.53</v>
       </c>
       <c r="D2">
-        <v>0.219</v>
+        <v>0.372</v>
       </c>
       <c r="E2">
-        <v>-17023.8</v>
+        <v>16908.6</v>
       </c>
       <c r="F2">
-        <v>439379.8</v>
+        <v>394049.8</v>
       </c>
       <c r="G2">
-        <v>30.27</v>
+        <v>30.23</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -521,31 +506,31 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>6.49</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>8.380000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="D3">
-        <v>0.168</v>
+        <v>-0.018</v>
       </c>
       <c r="E3">
-        <v>162485.9</v>
+        <v>127480.1</v>
       </c>
       <c r="F3">
-        <v>423831</v>
+        <v>485549.5</v>
       </c>
       <c r="G3">
-        <v>28.29</v>
+        <v>27.58</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -553,95 +538,31 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>7.62</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="C4">
-        <v>9.74</v>
+        <v>10.09</v>
       </c>
       <c r="D4">
-        <v>-0.135</v>
+        <v>-0.237</v>
       </c>
       <c r="E4">
-        <v>135008.3</v>
+        <v>36532.8</v>
       </c>
       <c r="F4">
-        <v>512672.4</v>
+        <v>548718.7</v>
       </c>
       <c r="G4">
-        <v>28</v>
+        <v>22.46</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>7.95</v>
-      </c>
-      <c r="C5">
-        <v>10.14</v>
-      </c>
-      <c r="D5">
-        <v>-0.146</v>
-      </c>
-      <c r="E5">
-        <v>36022.2</v>
-      </c>
-      <c r="F5">
-        <v>534534.7</v>
-      </c>
-      <c r="G5">
-        <v>34.9</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>7.32</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>-0.172</v>
-      </c>
-      <c r="E6">
-        <v>133994.4</v>
-      </c>
-      <c r="F6">
-        <v>521807.5</v>
-      </c>
-      <c r="G6">
-        <v>31.94</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
